--- a/resources/templates/商品资料模板.xlsx
+++ b/resources/templates/商品资料模板.xlsx
@@ -921,7 +921,7 @@
     </x:row>
     <x:row r="3" ht="92" customHeight="1">
       <x:c r="A3" s="54" t="str">
-        <x:v>一行填一种，比如“紫色＋大号”，每行分别填价格和库存，编码和图片可选填。
+        <x:v>一行填一种，比如“紫色＋大号”，每行分别填价格和库存，编码可选填，规格图按目标类目要求提供；后台标为必填时须补齐。
 “区分方式”填颜色、尺寸或容量；“具体选项”填紫色、大号或20L。每行的区分方式和顺序要一致。
 只有颜色可选时，后两列留空；商品没有可选款式时，这四列都可留空。规格图左上角放在 I 列对应格内。
 预留20行不够用时，复制最后一行继续填，最多100行；实际可填多少款，执行前按店铺类目核对。</x:v>
